--- a/data/2.b_Hybrider_Netzzugang_2035_5%/Global_Parameters.xlsx
+++ b/data/2.b_Hybrider_Netzzugang_2035_5%/Global_Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\2.b_Hybrider_Netzzugang\1_Model\2.b_Hybrider_Netzzugang_2035\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\LEGO-Pyomo\data\2.b_Hybrider_Netzzugang_2035_5%\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B3F003-4715-4F62-B325-4D774728F0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061B780C-E2FC-4B3C-8C00-94FECE29B261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72850" yWindow="2170" windowWidth="38620" windowHeight="21100" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="2900" windowWidth="19580" windowHeight="17880" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Parameters" sheetId="121" r:id="rId1"/>
@@ -59,12 +59,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>[h]</t>
   </si>
@@ -214,6 +217,9 @@
   </si>
   <si>
     <t>gurobi</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -855,25 +861,25 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="B1:H26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="31" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.06640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.09765625" style="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="120.86328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.86328125" style="1"/>
+    <col min="6" max="6" width="120.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
@@ -893,7 +899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
@@ -905,7 +911,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
@@ -925,12 +931,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
@@ -941,12 +947,12 @@
       <c r="F7" s="11"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>8</v>
@@ -961,12 +967,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
@@ -976,7 +982,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
@@ -988,7 +994,7 @@
       <c r="G11" s="11"/>
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1008,12 +1014,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
@@ -1024,7 +1030,7 @@
       <c r="F14" s="11"/>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="17" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>37</v>
       </c>
@@ -1052,7 +1058,7 @@
       <c r="F17" s="12"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
@@ -1063,7 +1069,7 @@
       <c r="F18" s="11"/>
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="2:8" ht="18.7" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -1083,7 +1089,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="21" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>40</v>
       </c>
@@ -1091,7 +1097,7 @@
       <c r="F21" s="12"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
         <v>41</v>
       </c>
@@ -1102,7 +1108,7 @@
       <c r="F22" s="11"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
@@ -1122,7 +1128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
         <v>45</v>
       </c>
@@ -1133,7 +1139,7 @@
       <c r="F25" s="11"/>
       <c r="H25" s="13"/>
     </row>
-    <row r="26" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
@@ -1225,12 +1231,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004934E3CB1C58BA43BC6E229E2BF20201" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e33ccc94e63df24f58cb47229b46e190">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87003a75-b64f-4b22-bf19-aa30740e3d46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f0f7a5bb162b669de9ce8ff8278c29f" ns2:_="">
     <xsd:import namespace="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
@@ -1376,6 +1376,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1386,22 +1392,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{773946F7-566C-458F-95C9-79B0CCE20E87}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1419,6 +1409,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
   <ds:schemaRefs>
